--- a/Provodnik/_шаблоны/Ф6_Msk.xlsx
+++ b/Provodnik/_шаблоны/Ф6_Msk.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="60" windowWidth="20490" windowHeight="7695"/>
@@ -14,7 +14,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'6.07'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'6.07'!$A$1:$K$12</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -1081,6 +1081,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F10:G10"/>
@@ -1090,11 +1095,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="94" orientation="landscape" r:id="rId1"/>
